--- a/interpolacao_curva_crushing.xlsx
+++ b/interpolacao_curva_crushing.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{440F013B-A210-41DF-9CE9-AC60F842C1EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA989446-5FF8-482B-9FDE-CDB9AEF3254D}"/>
   <bookViews>
-    <workbookView xWindow="690" yWindow="0" windowWidth="25110" windowHeight="20985" xr2:uid="{212263FA-FE73-45C6-A318-1EB70329A50B}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{212263FA-FE73-45C6-A318-1EB70329A50B}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -2535,6 +2535,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
